--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91478</v>
+        <v>91488</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91488</v>
+        <v>91500</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91504</v>
+        <v>91510</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11898,7 +11898,7 @@
         <v>121205311</v>
       </c>
       <c r="B89" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12012,6 +12012,653 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>123502587</v>
+      </c>
+      <c r="B90" t="n">
+        <v>77108</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>359348</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6224857</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>123502502</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79152</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>359477</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6224878</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>123502590</v>
+      </c>
+      <c r="B92" t="n">
+        <v>74767</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1458</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Grå skärelav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Dendrographa decolorans</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>359348</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6224857</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>123502602</v>
+      </c>
+      <c r="B93" t="n">
+        <v>74716</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1116</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Orangepudrad klotterlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alyxoria ochrocheila</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>359348</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6224857</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>123502485</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78092</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>145</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Klosterlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Biatoridium monasteriense</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>J.Lahm ex Körb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>359477</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6224878</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>123502644</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94661</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skuggsprötmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Eurhynchium striatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>359377</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6225019</v>
+      </c>
+      <c r="S95" t="n">
+        <v>50</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12014,10 +12014,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502587</v>
+        <v>123502590</v>
       </c>
       <c r="B90" t="n">
-        <v>77108</v>
+        <v>74767</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12026,25 +12026,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>1458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12120,10 +12120,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502502</v>
+        <v>123502602</v>
       </c>
       <c r="B91" t="n">
-        <v>79152</v>
+        <v>74716</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12132,25 +12132,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6431</v>
+        <v>1116</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12163,13 +12163,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R91" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12199,6 +12199,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12226,10 +12231,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502590</v>
+        <v>123502502</v>
       </c>
       <c r="B92" t="n">
-        <v>74767</v>
+        <v>79152</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12242,21 +12247,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1458</v>
+        <v>6431</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12269,13 +12274,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R92" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12332,10 +12337,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123502602</v>
+        <v>123502644</v>
       </c>
       <c r="B93" t="n">
-        <v>74716</v>
+        <v>94661</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12344,30 +12349,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1116</v>
+        <v>2755</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12375,13 +12381,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>359348</v>
+        <v>359377</v>
       </c>
       <c r="R93" t="n">
-        <v>6224857</v>
+        <v>6225019</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12411,11 +12417,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12443,10 +12444,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502485</v>
+        <v>123502587</v>
       </c>
       <c r="B94" t="n">
-        <v>78092</v>
+        <v>77108</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12455,25 +12456,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>145</v>
+        <v>1342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12486,13 +12487,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R94" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12522,11 +12523,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12554,10 +12550,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123502644</v>
+        <v>123502485</v>
       </c>
       <c r="B95" t="n">
-        <v>94661</v>
+        <v>78092</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12566,31 +12562,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2755</v>
+        <v>145</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12598,13 +12593,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>359377</v>
+        <v>359477</v>
       </c>
       <c r="R95" t="n">
-        <v>6225019</v>
+        <v>6224878</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12634,6 +12629,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12017,7 +12017,7 @@
         <v>123502587</v>
       </c>
       <c r="B90" t="n">
-        <v>77111</v>
+        <v>77117</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502644</v>
+        <v>123502485</v>
       </c>
       <c r="B91" t="n">
-        <v>94664</v>
+        <v>78101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12132,31 +12132,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2755</v>
+        <v>145</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12164,13 +12163,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359377</v>
+        <v>359477</v>
       </c>
       <c r="R91" t="n">
-        <v>6225019</v>
+        <v>6224878</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12200,6 +12199,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12227,10 +12231,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502602</v>
+        <v>123502502</v>
       </c>
       <c r="B92" t="n">
-        <v>74719</v>
+        <v>79161</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12239,25 +12243,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1116</v>
+        <v>6431</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12270,13 +12274,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R92" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12306,11 +12310,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12338,10 +12337,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123502590</v>
+        <v>123502644</v>
       </c>
       <c r="B93" t="n">
-        <v>74770</v>
+        <v>94681</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12354,26 +12353,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1458</v>
+        <v>2755</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12381,13 +12381,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>359348</v>
+        <v>359377</v>
       </c>
       <c r="R93" t="n">
-        <v>6224857</v>
+        <v>6225019</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12444,10 +12444,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502502</v>
+        <v>123502602</v>
       </c>
       <c r="B94" t="n">
-        <v>79155</v>
+        <v>74725</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12456,25 +12456,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6431</v>
+        <v>1116</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12487,13 +12487,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R94" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12523,6 +12523,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12550,10 +12555,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123502485</v>
+        <v>123502590</v>
       </c>
       <c r="B95" t="n">
-        <v>78095</v>
+        <v>74776</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12562,25 +12567,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>145</v>
+        <v>1458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12593,13 +12598,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R95" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12629,11 +12634,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12444,10 +12444,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502602</v>
+        <v>123502590</v>
       </c>
       <c r="B94" t="n">
-        <v>74725</v>
+        <v>74776</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12456,25 +12456,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1116</v>
+        <v>1458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12525,11 +12525,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12555,10 +12550,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123502590</v>
+        <v>123502602</v>
       </c>
       <c r="B95" t="n">
-        <v>74776</v>
+        <v>74725</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12567,25 +12562,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1458</v>
+        <v>1116</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12634,6 +12629,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12444,10 +12444,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502590</v>
+        <v>123502602</v>
       </c>
       <c r="B94" t="n">
-        <v>74776</v>
+        <v>74725</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12456,25 +12456,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1458</v>
+        <v>1116</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12525,6 +12525,11 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -12550,10 +12555,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123502602</v>
+        <v>123502590</v>
       </c>
       <c r="B95" t="n">
-        <v>74725</v>
+        <v>74776</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12562,25 +12567,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1116</v>
+        <v>1458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12629,11 +12634,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12017,7 +12017,7 @@
         <v>123502587</v>
       </c>
       <c r="B90" t="n">
-        <v>77117</v>
+        <v>77122</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502485</v>
+        <v>123502502</v>
       </c>
       <c r="B91" t="n">
-        <v>78101</v>
+        <v>79166</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12132,25 +12132,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>145</v>
+        <v>6431</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12201,11 +12201,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12231,10 +12226,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502502</v>
+        <v>123502485</v>
       </c>
       <c r="B92" t="n">
-        <v>79161</v>
+        <v>78106</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12243,25 +12238,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6431</v>
+        <v>145</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12312,6 +12307,11 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>123502644</v>
       </c>
       <c r="B93" t="n">
-        <v>94681</v>
+        <v>94687</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>123502602</v>
       </c>
       <c r="B94" t="n">
-        <v>74725</v>
+        <v>74728</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>123502590</v>
       </c>
       <c r="B95" t="n">
-        <v>74776</v>
+        <v>74779</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11648,10 +11648,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113800163</v>
+        <v>116504820</v>
       </c>
       <c r="B87" t="n">
-        <v>56918</v>
+        <v>97795</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11660,49 +11660,61 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102966</v>
+        <v>219864</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Turköp P14 (Vinterfågelräkningen), Västraby, Sk</t>
+          <t>Sankt Pers Nycklar, Sk</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>359483</v>
+        <v>359243</v>
       </c>
       <c r="R87" t="n">
-        <v>6225258</v>
+        <v>6224948</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11726,22 +11738,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>08:50</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:50</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11750,32 +11752,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Christer Strid</t>
+          <t>Karl-Erik Söderqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Christer Strid, Åsa Orrliden Strid</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Vinterfågelräkning</t>
-        </is>
-      </c>
+          <t>Karl-Erik Söderqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>116504820</v>
+        <v>121205311</v>
       </c>
       <c r="B88" t="n">
-        <v>97795</v>
+        <v>91511</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11784,61 +11783,52 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219864</v>
+        <v>2014</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sankt Pers Nycklar, Sk</t>
+          <t>Koralltaggsvamp, Västraby, Sk</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>359243</v>
+        <v>359677</v>
       </c>
       <c r="R88" t="n">
-        <v>6224948</v>
+        <v>6224588</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11862,12 +11852,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På boklåga i Tursköpsskogens Naturreservat</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11895,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121205311</v>
+        <v>123502502</v>
       </c>
       <c r="B89" t="n">
-        <v>91511</v>
+        <v>79168</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11907,52 +11902,44 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2014</v>
+        <v>6431</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp, Västraby, Sk</t>
+          <t>Tursköpsskogen, Sk</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>359677</v>
+        <v>359477</v>
       </c>
       <c r="R89" t="n">
-        <v>6224588</v>
+        <v>6224878</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11976,17 +11963,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På boklåga i Tursköpsskogens Naturreservat</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12002,22 +11984,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Karl-Erik Söderqvist</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Karl-Erik Söderqvist</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502587</v>
+        <v>123502590</v>
       </c>
       <c r="B90" t="n">
-        <v>77122</v>
+        <v>74780</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12026,25 +12008,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>1458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12120,10 +12102,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502502</v>
+        <v>123502587</v>
       </c>
       <c r="B91" t="n">
-        <v>79166</v>
+        <v>77124</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12132,25 +12114,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12163,13 +12145,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R91" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12229,7 +12211,7 @@
         <v>123502485</v>
       </c>
       <c r="B92" t="n">
-        <v>78106</v>
+        <v>78108</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12340,7 +12322,7 @@
         <v>123502644</v>
       </c>
       <c r="B93" t="n">
-        <v>94687</v>
+        <v>94689</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12447,7 +12429,7 @@
         <v>123502602</v>
       </c>
       <c r="B94" t="n">
-        <v>74728</v>
+        <v>74729</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12553,112 +12535,6 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>123502590</v>
-      </c>
-      <c r="B95" t="n">
-        <v>74779</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1458</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Grå skärelav</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Dendrographa decolorans</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Tursköpsskogen, Sk</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>359348</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6224857</v>
-      </c>
-      <c r="S95" t="n">
-        <v>25</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Helsingborg</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Kattarp</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Lars Salomon</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Lars Salomon</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11890,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123502502</v>
+        <v>123502602</v>
       </c>
       <c r="B89" t="n">
-        <v>79168</v>
+        <v>74729</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11902,25 +11902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6431</v>
+        <v>1116</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11933,13 +11933,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R89" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11969,6 +11969,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11996,10 +12001,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502590</v>
+        <v>123502587</v>
       </c>
       <c r="B90" t="n">
-        <v>74780</v>
+        <v>77124</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12008,25 +12013,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1458</v>
+        <v>1342</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12102,10 +12107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502587</v>
+        <v>123502502</v>
       </c>
       <c r="B91" t="n">
-        <v>77124</v>
+        <v>79168</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12114,25 +12119,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12145,13 +12150,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R91" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12322,7 +12327,7 @@
         <v>123502644</v>
       </c>
       <c r="B93" t="n">
-        <v>94689</v>
+        <v>95197</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12426,10 +12431,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502602</v>
+        <v>123502590</v>
       </c>
       <c r="B94" t="n">
-        <v>74729</v>
+        <v>74780</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12438,25 +12443,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1116</v>
+        <v>1458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12505,11 +12510,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11890,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123502602</v>
+        <v>123502587</v>
       </c>
       <c r="B89" t="n">
-        <v>74729</v>
+        <v>77124</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11906,21 +11906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11971,11 +11971,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -12001,10 +11996,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502587</v>
+        <v>123502602</v>
       </c>
       <c r="B90" t="n">
-        <v>77124</v>
+        <v>74729</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12017,21 +12012,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>1116</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12082,6 +12077,11 @@
           <t>2025-03-26</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12107,10 +12107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502502</v>
+        <v>123502590</v>
       </c>
       <c r="B91" t="n">
-        <v>79168</v>
+        <v>74780</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12123,21 +12123,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6431</v>
+        <v>1458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R91" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12213,10 +12213,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502485</v>
+        <v>123502502</v>
       </c>
       <c r="B92" t="n">
-        <v>78108</v>
+        <v>79168</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12225,25 +12225,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>145</v>
+        <v>6431</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12292,11 +12292,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12431,10 +12426,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502590</v>
+        <v>123502485</v>
       </c>
       <c r="B94" t="n">
-        <v>74780</v>
+        <v>78108</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12443,25 +12438,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1458</v>
+        <v>145</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12474,13 +12469,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R94" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12510,6 +12505,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11890,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123502587</v>
+        <v>123502502</v>
       </c>
       <c r="B89" t="n">
-        <v>77124</v>
+        <v>79168</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11902,25 +11902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11933,13 +11933,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R89" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12107,10 +12107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502590</v>
+        <v>123502644</v>
       </c>
       <c r="B91" t="n">
-        <v>74780</v>
+        <v>95197</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12123,26 +12123,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1458</v>
+        <v>2755</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12150,13 +12151,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359348</v>
+        <v>359377</v>
       </c>
       <c r="R91" t="n">
-        <v>6224857</v>
+        <v>6225019</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12213,10 +12214,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502502</v>
+        <v>123502587</v>
       </c>
       <c r="B92" t="n">
-        <v>79168</v>
+        <v>77124</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12225,25 +12226,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12256,13 +12257,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R92" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12319,10 +12320,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123502644</v>
+        <v>123502485</v>
       </c>
       <c r="B93" t="n">
-        <v>95197</v>
+        <v>78108</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12331,31 +12332,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2755</v>
+        <v>145</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12363,13 +12363,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>359377</v>
+        <v>359477</v>
       </c>
       <c r="R93" t="n">
-        <v>6225019</v>
+        <v>6224878</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12399,6 +12399,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12426,10 +12431,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502485</v>
+        <v>123502590</v>
       </c>
       <c r="B94" t="n">
-        <v>78108</v>
+        <v>74780</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12438,25 +12443,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>145</v>
+        <v>1458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12469,13 +12474,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R94" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12505,11 +12510,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11890,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123502502</v>
+        <v>123502602</v>
       </c>
       <c r="B89" t="n">
-        <v>79168</v>
+        <v>74729</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11902,25 +11902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6431</v>
+        <v>1116</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11933,13 +11933,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R89" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11969,6 +11969,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11996,10 +12001,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502602</v>
+        <v>123502590</v>
       </c>
       <c r="B90" t="n">
-        <v>74729</v>
+        <v>74780</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12008,25 +12013,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1116</v>
+        <v>1458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12077,11 +12082,6 @@
           <t>2025-03-26</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12107,10 +12107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502644</v>
+        <v>123502502</v>
       </c>
       <c r="B91" t="n">
-        <v>95197</v>
+        <v>79168</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12123,27 +12123,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2755</v>
+        <v>6431</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12151,13 +12150,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359377</v>
+        <v>359477</v>
       </c>
       <c r="R91" t="n">
-        <v>6225019</v>
+        <v>6224878</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12214,10 +12213,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502587</v>
+        <v>123502644</v>
       </c>
       <c r="B92" t="n">
-        <v>77124</v>
+        <v>95197</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12226,30 +12225,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1342</v>
+        <v>2755</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12257,13 +12257,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359348</v>
+        <v>359377</v>
       </c>
       <c r="R92" t="n">
-        <v>6224857</v>
+        <v>6225019</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12431,10 +12431,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502590</v>
+        <v>123502587</v>
       </c>
       <c r="B94" t="n">
-        <v>74780</v>
+        <v>77124</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12443,25 +12443,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1458</v>
+        <v>1342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12107,10 +12107,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502502</v>
+        <v>123502644</v>
       </c>
       <c r="B91" t="n">
-        <v>79168</v>
+        <v>95197</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12123,26 +12123,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6431</v>
+        <v>2755</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12150,13 +12151,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359477</v>
+        <v>359377</v>
       </c>
       <c r="R91" t="n">
-        <v>6224878</v>
+        <v>6225019</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12213,10 +12214,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502644</v>
+        <v>123502502</v>
       </c>
       <c r="B92" t="n">
-        <v>95197</v>
+        <v>79168</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12229,27 +12230,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2755</v>
+        <v>6431</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12257,13 +12257,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359377</v>
+        <v>359477</v>
       </c>
       <c r="R92" t="n">
-        <v>6225019</v>
+        <v>6224878</v>
       </c>
       <c r="S92" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -11890,10 +11890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123502602</v>
+        <v>123502502</v>
       </c>
       <c r="B89" t="n">
-        <v>74729</v>
+        <v>79168</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11902,25 +11902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1116</v>
+        <v>6431</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11933,13 +11933,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R89" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11969,11 +11969,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12001,10 +11996,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123502590</v>
+        <v>123502644</v>
       </c>
       <c r="B90" t="n">
-        <v>74780</v>
+        <v>95197</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12017,26 +12012,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1458</v>
+        <v>2755</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -12044,13 +12040,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>359348</v>
+        <v>359377</v>
       </c>
       <c r="R90" t="n">
-        <v>6224857</v>
+        <v>6225019</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12107,10 +12103,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123502644</v>
+        <v>123502590</v>
       </c>
       <c r="B91" t="n">
-        <v>95197</v>
+        <v>74780</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12123,27 +12119,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2755</v>
+        <v>1458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12151,13 +12146,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>359377</v>
+        <v>359348</v>
       </c>
       <c r="R91" t="n">
-        <v>6225019</v>
+        <v>6224857</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12214,10 +12209,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123502502</v>
+        <v>123502587</v>
       </c>
       <c r="B92" t="n">
-        <v>79168</v>
+        <v>77124</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12226,25 +12221,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -12257,13 +12252,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R92" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12320,10 +12315,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123502485</v>
+        <v>123502602</v>
       </c>
       <c r="B93" t="n">
-        <v>78108</v>
+        <v>74729</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12332,25 +12327,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>145</v>
+        <v>1116</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12363,13 +12358,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>359477</v>
+        <v>359348</v>
       </c>
       <c r="R93" t="n">
-        <v>6224878</v>
+        <v>6224857</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12403,7 +12398,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
+          <t>På vedblotta på hassel</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12431,10 +12426,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123502587</v>
+        <v>123502485</v>
       </c>
       <c r="B94" t="n">
-        <v>77124</v>
+        <v>78108</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12443,25 +12438,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1342</v>
+        <v>145</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12474,13 +12469,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>359348</v>
+        <v>359477</v>
       </c>
       <c r="R94" t="n">
-        <v>6224857</v>
+        <v>6224878</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12510,6 +12505,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På ask med kräfta. Trädet som tyvärr är döende växer i en stenmur i brynet mot NO. På västra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12535,6 +12535,115 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125920221</v>
+      </c>
+      <c r="B95" t="n">
+        <v>58186</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Fd P-plats Tursköpsskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>359509</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6225239</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Helsingborg</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Kattarp</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Liselotte Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Liselotte Andersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12540,7 +12540,7 @@
         <v>125920221</v>
       </c>
       <c r="B95" t="n">
-        <v>58186</v>
+        <v>58187</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12540,7 +12540,7 @@
         <v>125920221</v>
       </c>
       <c r="B95" t="n">
-        <v>58187</v>
+        <v>58188</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12540,7 +12540,7 @@
         <v>125920221</v>
       </c>
       <c r="B95" t="n">
-        <v>58188</v>
+        <v>58192</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 53008-2019 artfynd.xlsx
+++ b/artfynd/A 53008-2019 artfynd.xlsx
@@ -12540,7 +12540,7 @@
         <v>125920221</v>
       </c>
       <c r="B95" t="n">
-        <v>58192</v>
+        <v>58195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
